--- a/templates/PhieuKetQuaOnlinePDF.xlsx
+++ b/templates/PhieuKetQuaOnlinePDF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E0C871-F774-6A4F-B360-C64329AA8848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBDD7CD-933B-6342-9B7D-A9A5326BDDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2600" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,7 +145,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -194,11 +194,6 @@
       <name val="Myriad pro"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="Myriad pro"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="12"/>
       <name val="Myriad pro"/>
@@ -262,17 +257,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -285,6 +269,29 @@
     <font>
       <sz val="13"/>
       <color rgb="FF0000FF"/>
+      <name val="Myriad pro"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Myriad pro"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Myriad pro"/>
     </font>
   </fonts>
@@ -349,24 +356,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -375,24 +381,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -401,17 +405,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -501,7 +508,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>673100</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>168274</xdr:rowOff>
     </xdr:to>
@@ -574,8 +581,8 @@
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1511300</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
@@ -967,10 +974,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="0.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="38" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="0.33203125" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="256" width="9.1640625" style="1"/>
@@ -1481,22 +1488,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" spans="1:7" ht="6.75" customHeight="1">
       <c r="C3" s="2"/>
@@ -1506,25 +1513,25 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1">
       <c r="B4" s="2"/>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1">
       <c r="B5" s="2"/>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="1:7" ht="10.5" customHeight="1">
       <c r="C6" s="2"/>
@@ -1533,14 +1540,14 @@
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
     </row>
     <row r="8" spans="1:7" ht="5.25" customHeight="1">
       <c r="A8" s="4"/>
@@ -1551,265 +1558,265 @@
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="32" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="38"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="32" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="35"/>
+      <c r="F10" s="37"/>
     </row>
     <row r="11" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="32" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="35"/>
-    </row>
-    <row r="12" spans="1:7" s="10" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8" t="s">
+      <c r="F11" s="37"/>
+    </row>
+    <row r="12" spans="1:7" s="9" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
     </row>
     <row r="13" spans="1:7" ht="4.5" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="5" customFormat="1" ht="19" customHeight="1">
-      <c r="A15" s="14"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="15" t="b">
+      <c r="A15" s="13"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1">
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="14"/>
     </row>
     <row r="17" spans="2:6" ht="18" customHeight="1">
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="21"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="2:6" ht="18" customHeight="1">
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="23"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" spans="2:6" ht="18" customHeight="1">
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="23"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="22"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="23"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="22"/>
     </row>
     <row r="21" spans="2:6" ht="18" customHeight="1">
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="23"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" spans="2:6" ht="18" customHeight="1">
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="21"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="2:6" ht="18" customHeight="1">
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="E23" s="20"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="2:6" ht="18" customHeight="1">
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="E24" s="20"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="2:6" ht="18" customHeight="1">
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="E25" s="20"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="2:6" ht="18" customHeight="1">
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="E26" s="20"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="2:6" ht="18" customHeight="1">
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="E27" s="20"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" spans="2:6" ht="18" customHeight="1">
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="E28" s="20"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" spans="2:6" ht="18" customHeight="1">
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="E29" s="20"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" spans="2:6" ht="18" customHeight="1">
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="E30" s="20"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" spans="2:6" ht="18" customHeight="1">
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="E31" s="20"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="2:6" ht="18" customHeight="1">
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="E32" s="20"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="2:5" ht="18" customHeight="1">
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="E33" s="19"/>
     </row>
     <row r="34" spans="2:5" ht="18" customHeight="1">
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="E34" s="19"/>
     </row>
     <row r="35" spans="2:5" ht="18" customHeight="1">
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="E35" s="20"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="E35" s="19"/>
     </row>
     <row r="36" spans="2:5" ht="18" customHeight="1">
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="E36" s="20"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="E36" s="19"/>
     </row>
     <row r="37" spans="2:5" ht="18" customHeight="1">
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="E37" s="19"/>
     </row>
     <row r="38" spans="2:5" ht="18" customHeight="1">
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="E38" s="19"/>
     </row>
     <row r="39" spans="2:5" ht="18" customHeight="1">
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="E39" s="20"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="E39" s="19"/>
     </row>
     <row r="40" spans="2:5" ht="18" customHeight="1">
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="E40" s="20"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="E40" s="19"/>
     </row>
     <row r="41" spans="2:5" ht="18" customHeight="1">
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="E41" s="20"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="E41" s="19"/>
     </row>
     <row r="42" spans="2:5" ht="18" customHeight="1">
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="E42" s="20"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="E42" s="19"/>
     </row>
     <row r="43" spans="2:5" ht="18" customHeight="1">
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="E43" s="20"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="E43" s="19"/>
     </row>
     <row r="44" spans="2:5" ht="18" customHeight="1">
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="E44" s="19"/>
     </row>
     <row r="45" spans="2:5" ht="18" customHeight="1">
-      <c r="E45" s="20"/>
+      <c r="E45" s="19"/>
     </row>
     <row r="46" spans="2:5" ht="18" customHeight="1">
-      <c r="E46" s="20"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="2:5" ht="18" customHeight="1">
-      <c r="E47" s="20"/>
+      <c r="E47" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/templates/PhieuKetQuaOnlinePDF.xlsx
+++ b/templates/PhieuKetQuaOnlinePDF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBDD7CD-933B-6342-9B7D-A9A5326BDDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FFD3BF-FD59-CA41-9EA7-2170F377F58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2600" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t xml:space="preserve">                PHÒNG XÉT NGHIỆM Y KHOA ANH QUÂN</t>
   </si>
   <si>
-    <t xml:space="preserve">                        60 Đống Đa, Phường 2, TP. Cao Lãnh, Đồng Tháp.</t>
-  </si>
-  <si>
     <t>PHIẾU KẾT QUẢ XÉT NGHIỆM</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
       </rPr>
       <t>laboanhquan@gmail.com</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                        60 Đống Đa, Phường Cao Lãnh, Đồng Tháp.</t>
   </si>
 </sst>
 </file>
@@ -399,26 +399,26 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1488,22 +1488,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
-      <c r="B2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="6.75" customHeight="1">
       <c r="C3" s="2"/>
@@ -1514,24 +1514,24 @@
     <row r="4" spans="1:7" ht="18" customHeight="1">
       <c r="B4" s="2"/>
       <c r="C4" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
+        <v>22</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1">
       <c r="B5" s="2"/>
       <c r="C5" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+        <v>23</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
     </row>
     <row r="6" spans="1:7" ht="10.5" customHeight="1">
       <c r="C6" s="2"/>
@@ -1540,14 +1540,14 @@
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
+      <c r="A7" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
     </row>
     <row r="8" spans="1:7" ht="5.25" customHeight="1">
       <c r="A8" s="4"/>
@@ -1558,59 +1558,59 @@
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="E9" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="38"/>
+    </row>
+    <row r="10" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
+      <c r="B10" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="34" t="s">
+      <c r="D10" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="35"/>
-    </row>
-    <row r="10" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="B10" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="36" t="s">
+      <c r="F10" s="35"/>
+    </row>
+    <row r="11" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
+      <c r="B11" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="37"/>
-    </row>
-    <row r="11" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="B11" s="32" t="s">
+      <c r="D11" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="32" t="s">
+      <c r="E11" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="37"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:7" s="9" customFormat="1" ht="18.75" customHeight="1">
       <c r="A12" s="8"/>
-      <c r="B12" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
+      <c r="B12" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:7" ht="4.5" customHeight="1">
       <c r="A13" s="10"/>
@@ -1623,19 +1623,19 @@
     <row r="14" spans="1:7" ht="30" customHeight="1">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="D14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>14</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="5" customFormat="1" ht="19" customHeight="1">
